--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135672536</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135674263</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135674341</v>
       </c>
       <c r="B5" t="n">
-        <v>92731</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,32 +1138,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135672727</v>
+        <v>135673240</v>
       </c>
       <c r="B6" t="n">
-        <v>92601</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468803</v>
+        <v>468896</v>
       </c>
       <c r="R6" t="n">
-        <v>7020322</v>
+        <v>7020492</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grannlaga.</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,38 +1244,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672727</t>
+          <t>https://artportalen.se/Sighting/135673240</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135673240</v>
+        <v>135672863</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468896</v>
+        <v>468807</v>
       </c>
       <c r="R7" t="n">
-        <v>7020492</v>
+        <v>7020357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,51 +1356,56 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135673240</t>
+          <t>https://artportalen.se/Sighting/135672863</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135672863</v>
+        <v>135672992</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Harptjärnen, Harptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468807</v>
+        <v>468859</v>
       </c>
       <c r="R8" t="n">
-        <v>7020357</v>
+        <v>7020418</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bearbetad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,13 +1478,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672863</t>
+          <t>https://artportalen.se/Sighting/135672992</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135672992</v>
+        <v>135674237</v>
       </c>
       <c r="B9" t="n">
         <v>57977</v>
@@ -1519,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468859</v>
+        <v>468908</v>
       </c>
       <c r="R9" t="n">
-        <v>7020418</v>
+        <v>7020440</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,12 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetad gran</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,33 +1595,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672992</t>
+          <t>https://artportalen.se/Sighting/135674237</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135674237</v>
+        <v>135672806</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468908</v>
+        <v>468804</v>
       </c>
       <c r="R10" t="n">
-        <v>7020440</v>
+        <v>7020338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,13 +1717,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135674237</t>
+          <t>https://artportalen.se/Sighting/135672806</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135672806</v>
+        <v>135673699</v>
       </c>
       <c r="B11" t="n">
         <v>57980</v>
@@ -1749,7 +1754,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1758,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468804</v>
+        <v>468977</v>
       </c>
       <c r="R11" t="n">
-        <v>7020338</v>
+        <v>7020411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Barkfläkt gran.</t>
+          <t>Ringhackad och barkfläkta granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,13 +1839,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672806</t>
+          <t>https://artportalen.se/Sighting/135673699</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135673699</v>
+        <v>135674646</v>
       </c>
       <c r="B12" t="n">
         <v>57980</v>
@@ -1880,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468977</v>
+        <v>468841</v>
       </c>
       <c r="R12" t="n">
-        <v>7020411</v>
+        <v>7020433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,12 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhackad och barkfläkta granar.</t>
+          <t>Skalad klen gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,13 +1961,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135673699</t>
+          <t>https://artportalen.se/Sighting/135674646</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135674646</v>
+        <v>135674814</v>
       </c>
       <c r="B13" t="n">
         <v>57980</v>
@@ -1993,19 +1998,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Harptjärnen, Harptjärnen, Jmt</t>
+          <t>Kattbacktjärnen, Kattbacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468841</v>
+        <v>468789</v>
       </c>
       <c r="R13" t="n">
-        <v>7020433</v>
+        <v>7020392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,12 +2052,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Skalad klen gran</t>
+          <t>Barkfläkt klen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,56 +2083,65 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135674646</t>
+          <t>https://artportalen.se/Sighting/135674814</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135674814</v>
+        <v>135674623</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>99173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kattbacktjärnen, Kattbacktjärnen, Jmt</t>
+          <t>Harptjärnen, Harptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468789</v>
+        <v>468841</v>
       </c>
       <c r="R14" t="n">
-        <v>7020392</v>
+        <v>7020433</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2173,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,12 +2183,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Barkfläkt klen gran</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,43 +2209,43 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135674814</t>
+          <t>https://artportalen.se/Sighting/135674623</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135674623</v>
+        <v>135672592</v>
       </c>
       <c r="B15" t="n">
-        <v>99146</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,7 +2255,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2255,10 +2264,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468841</v>
+        <v>468788</v>
       </c>
       <c r="R15" t="n">
-        <v>7020433</v>
+        <v>7020306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2299,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2300,7 +2309,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,16 +2335,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135674623</t>
+          <t>https://artportalen.se/Sighting/135672592</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135672592</v>
+        <v>135672776</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,7 +2371,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2381,10 +2390,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468788</v>
+        <v>468803</v>
       </c>
       <c r="R16" t="n">
-        <v>7020306</v>
+        <v>7020322</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2425,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2435,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,16 +2461,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672592</t>
+          <t>https://artportalen.se/Sighting/135672776</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135672776</v>
+        <v>135673308</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2497,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2507,10 +2516,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468803</v>
+        <v>468905</v>
       </c>
       <c r="R17" t="n">
-        <v>7020322</v>
+        <v>7020472</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2551,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,7 +2561,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,16 +2587,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672776</t>
+          <t>https://artportalen.se/Sighting/135673308</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135673308</v>
+        <v>135673524</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2623,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2633,10 +2642,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468905</v>
+        <v>468959</v>
       </c>
       <c r="R18" t="n">
-        <v>7020472</v>
+        <v>7020438</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,7 +2677,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,7 +2687,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,16 +2713,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135673308</t>
+          <t>https://artportalen.se/Sighting/135673524</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135673524</v>
+        <v>135673673</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,7 +2749,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2759,10 +2768,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468959</v>
+        <v>468958</v>
       </c>
       <c r="R19" t="n">
-        <v>7020438</v>
+        <v>7020434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2803,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,7 +2813,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt i området.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,16 +2844,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135673524</t>
+          <t>https://artportalen.se/Sighting/135673673</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135673673</v>
+        <v>135673826</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2866,7 +2880,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2885,10 +2899,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468958</v>
+        <v>469000</v>
       </c>
       <c r="R20" t="n">
-        <v>7020434</v>
+        <v>7020467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2920,7 +2934,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2930,12 +2944,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt i området.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2961,16 +2970,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135673673</t>
+          <t>https://artportalen.se/Sighting/135673826</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135673826</v>
+        <v>135674688</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +3006,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3012,14 +3021,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Harptjärnen, Harptjärnen, Jmt</t>
+          <t>Kattbacktjärnen, Kattbacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469000</v>
+        <v>468823</v>
       </c>
       <c r="R21" t="n">
-        <v>7020467</v>
+        <v>7020445</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3051,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3061,7 +3070,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,65 +3096,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135673826</t>
+          <t>https://artportalen.se/Sighting/135674688</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135674688</v>
+        <v>135673044</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>98320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kattbacktjärnen, Kattbacktjärnen, Jmt</t>
+          <t>Harptjärnen, Harptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468823</v>
+        <v>468853</v>
       </c>
       <c r="R22" t="n">
-        <v>7020445</v>
+        <v>7020418</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3177,7 +3172,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,7 +3182,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt utmed diket.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3212,123 +3212,6 @@
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135674688</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135673044</v>
-      </c>
-      <c r="B23" t="n">
-        <v>98293</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Harptjärnen, Harptjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>468853</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7020418</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt utmed diket.</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135673044</t>
         </is>
@@ -3357,7 +3240,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110238</v>
+        <v>110240</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100299</v>
+        <v>100301</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92765</v>
+        <v>92780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92765</v>
+        <v>92780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>135672863</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>135672992</v>
       </c>
       <c r="B17" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135674237</v>
       </c>
       <c r="B18" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135672806</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135673699</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135674646</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135674814</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135830780</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135831065</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135831554</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135831686</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>135831776</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135831853</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>135832038</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135832160</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>135832606</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>135832988</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135833057</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>135832935</v>
       </c>
       <c r="B34" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>135831003</v>
       </c>
       <c r="B35" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110240</v>
+        <v>110263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100301</v>
+        <v>100318</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>135672863</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110263</v>
+        <v>110265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100318</v>
+        <v>100320</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99318</v>
+        <v>99319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110265</v>
+        <v>110266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100320</v>
+        <v>100321</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>135672863</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>135672992</v>
       </c>
       <c r="B17" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135674237</v>
       </c>
       <c r="B18" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135672806</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135673699</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135674646</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135674814</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135830780</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135831065</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135831554</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135831686</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>135831776</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135831853</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>135832038</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135832160</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>135832606</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>135832988</v>
       </c>
       <c r="B32" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135833057</v>
       </c>
       <c r="B33" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>135832935</v>
       </c>
       <c r="B34" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>135831003</v>
       </c>
       <c r="B35" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110266</v>
+        <v>110267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100321</v>
+        <v>100322</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>135672863</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>135672992</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135674237</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135672806</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135673699</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135674646</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135674814</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135830780</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135831065</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135831554</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135831686</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>135831776</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135831853</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>135832038</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135832160</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>135832606</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>135832988</v>
       </c>
       <c r="B32" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135833057</v>
       </c>
       <c r="B33" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>135832935</v>
       </c>
       <c r="B34" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>135831003</v>
       </c>
       <c r="B35" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110267</v>
+        <v>110273</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100322</v>
+        <v>100328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135674592</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135672536</v>
       </c>
       <c r="B5" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135674263</v>
       </c>
       <c r="B6" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135674341</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135673240</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>135672863</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>135672992</v>
       </c>
       <c r="B17" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135674237</v>
       </c>
       <c r="B18" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135672806</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135673699</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135674646</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135674814</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135830780</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135831065</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135831554</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135831686</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>135831776</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135831853</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>135832038</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135832160</v>
       </c>
       <c r="B30" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>135832606</v>
       </c>
       <c r="B31" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>135832988</v>
       </c>
       <c r="B32" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135833057</v>
       </c>
       <c r="B33" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>135832935</v>
       </c>
       <c r="B34" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>135831003</v>
       </c>
       <c r="B35" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>135674623</v>
       </c>
       <c r="B40" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110273</v>
+        <v>110274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135672592</v>
       </c>
       <c r="B42" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>135672776</v>
       </c>
       <c r="B43" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>135673308</v>
       </c>
       <c r="B44" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135673524</v>
       </c>
       <c r="B45" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135673673</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>135673826</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135674688</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100328</v>
+        <v>100329</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>135673044</v>
       </c>
       <c r="B69" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92790</v>
+        <v>92796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>98335</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110274</v>
+        <v>110285</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100329</v>
+        <v>100340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92796</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135830780</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135831065</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135831554</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135831686</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>135831776</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135831853</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>135832038</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135832160</v>
       </c>
       <c r="B30" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>135832606</v>
       </c>
       <c r="B31" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>135832988</v>
       </c>
       <c r="B32" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135833057</v>
       </c>
       <c r="B33" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>135832935</v>
       </c>
       <c r="B34" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>135831003</v>
       </c>
       <c r="B35" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98335</v>
+        <v>98348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110285</v>
+        <v>110298</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100340</v>
+        <v>100353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92803</v>
+        <v>92804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110298</v>
+        <v>110299</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100353</v>
+        <v>100354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 30249-2026 artfynd.xlsx
+++ b/artfynd/A 30249-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135831567</v>
       </c>
       <c r="B3" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135831632</v>
       </c>
       <c r="B4" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135831957</v>
       </c>
       <c r="B8" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135830805</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135831446</v>
       </c>
       <c r="B11" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135831790</v>
       </c>
       <c r="B12" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>135831736</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135832104</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>135832329</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135830780</v>
       </c>
       <c r="B23" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135831065</v>
       </c>
       <c r="B24" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135831554</v>
       </c>
       <c r="B25" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135831686</v>
       </c>
       <c r="B26" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>135831776</v>
       </c>
       <c r="B27" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135831853</v>
       </c>
       <c r="B28" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>135832038</v>
       </c>
       <c r="B29" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>135832160</v>
       </c>
       <c r="B30" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>135832606</v>
       </c>
       <c r="B31" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>135832988</v>
       </c>
       <c r="B32" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135833057</v>
       </c>
       <c r="B33" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>135832935</v>
       </c>
       <c r="B34" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>135831003</v>
       </c>
       <c r="B35" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135831238</v>
       </c>
       <c r="B36" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>135832309</v>
       </c>
       <c r="B37" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>135831469</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>135831288</v>
       </c>
       <c r="B39" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135831256</v>
       </c>
       <c r="B41" t="n">
-        <v>110299</v>
+        <v>110312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>135830717</v>
       </c>
       <c r="B49" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>135830854</v>
       </c>
       <c r="B50" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>135831024</v>
       </c>
       <c r="B51" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135831194</v>
       </c>
       <c r="B52" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>135831500</v>
       </c>
       <c r="B53" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>135831528</v>
       </c>
       <c r="B54" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135831712</v>
       </c>
       <c r="B55" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>135831929</v>
       </c>
       <c r="B56" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>135832049</v>
       </c>
       <c r="B57" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>135832196</v>
       </c>
       <c r="B58" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135832406</v>
       </c>
       <c r="B59" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135832708</v>
       </c>
       <c r="B60" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135832863</v>
       </c>
       <c r="B61" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135833029</v>
       </c>
       <c r="B62" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135831323</v>
       </c>
       <c r="B63" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135832095</v>
       </c>
       <c r="B64" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>135831436</v>
       </c>
       <c r="B65" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>135831902</v>
       </c>
       <c r="B66" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>135831358</v>
       </c>
       <c r="B67" t="n">
-        <v>100354</v>
+        <v>100367</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>135831221</v>
       </c>
       <c r="B68" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
